--- a/files/Pruebas_Excel.xlsx
+++ b/files/Pruebas_Excel.xlsx
@@ -377,8 +377,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N86"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:N211"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="9.140625" customWidth="1" style="1" min="1" max="2"/>
     <col hidden="1" width="13" customWidth="1" style="5" min="3" max="3"/>
@@ -3736,14 +3736,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
         <v>150</v>
       </c>
       <c r="E67" t="n">
         <v>15</v>
       </c>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -3787,14 +3785,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
         <v>150</v>
       </c>
       <c r="E68" t="n">
         <v>15</v>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -3838,14 +3834,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
         <v>150</v>
       </c>
       <c r="E69" t="n">
         <v>15</v>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -3889,14 +3883,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="n">
         <v>150</v>
       </c>
       <c r="E70" t="n">
         <v>15</v>
       </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -3940,14 +3932,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
         <v>150</v>
       </c>
       <c r="E71" t="n">
         <v>15</v>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -3991,14 +3981,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
         <v>150</v>
       </c>
       <c r="E72" t="n">
         <v>15</v>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -4042,14 +4030,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
       <c r="D73" t="n">
         <v>150</v>
       </c>
       <c r="E73" t="n">
         <v>15</v>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -4093,14 +4079,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="n">
         <v>150</v>
       </c>
       <c r="E74" t="n">
         <v>15</v>
       </c>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -4144,14 +4128,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
         <v>150</v>
       </c>
       <c r="E75" t="n">
         <v>15</v>
       </c>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -4195,14 +4177,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
       <c r="D76" t="n">
         <v>150</v>
       </c>
       <c r="E76" t="n">
         <v>15</v>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -4246,14 +4226,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
         <v>150</v>
       </c>
       <c r="E77" t="n">
         <v>15</v>
       </c>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -4297,14 +4275,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
         <v>150</v>
       </c>
       <c r="E78" t="n">
         <v>15</v>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -4348,14 +4324,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="n">
         <v>150</v>
       </c>
       <c r="E79" t="n">
         <v>15</v>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -4399,14 +4373,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
       <c r="D80" t="n">
         <v>150</v>
       </c>
       <c r="E80" t="n">
         <v>15</v>
       </c>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -4450,14 +4422,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="n">
         <v>150</v>
       </c>
       <c r="E81" t="n">
         <v>15</v>
       </c>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -4501,14 +4471,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
       <c r="D82" t="n">
         <v>150</v>
       </c>
       <c r="E82" t="n">
         <v>15</v>
       </c>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -4552,14 +4520,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
         <v>150</v>
       </c>
       <c r="E83" t="n">
         <v>15</v>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -4603,14 +4569,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
         <v>150</v>
       </c>
       <c r="E84" t="n">
         <v>15</v>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -4654,14 +4618,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
         <v>150</v>
       </c>
       <c r="E85" t="n">
         <v>15</v>
       </c>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -4705,14 +4667,12 @@
           <t>HG137C20</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="n">
         <v>60</v>
       </c>
       <c r="E86" t="n">
         <v>6</v>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>Zapatera de Tela de 6 peldaños Doble de 118*25*104cm Vino</t>
@@ -4742,6 +4702,6251 @@
       <c r="M86" t="inlineStr">
         <is>
           <t>P034</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>HG16679</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>300</v>
+      </c>
+      <c r="E87" t="n">
+        <v>20</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L87" t="n">
+        <v>15</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>HG16680</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>300</v>
+      </c>
+      <c r="E88" t="n">
+        <v>20</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L88" t="n">
+        <v>15</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>HG16681</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>300</v>
+      </c>
+      <c r="E89" t="n">
+        <v>20</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L89" t="n">
+        <v>15</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>HG16682</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>300</v>
+      </c>
+      <c r="E90" t="n">
+        <v>20</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L90" t="n">
+        <v>15</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>HG16683</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>300</v>
+      </c>
+      <c r="E91" t="n">
+        <v>20</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L91" t="n">
+        <v>15</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>HG16684</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>300</v>
+      </c>
+      <c r="E92" t="n">
+        <v>20</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L92" t="n">
+        <v>15</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>HG16685</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>300</v>
+      </c>
+      <c r="E93" t="n">
+        <v>20</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L93" t="n">
+        <v>15</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>HG16686</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>300</v>
+      </c>
+      <c r="E94" t="n">
+        <v>20</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L94" t="n">
+        <v>15</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>HG16687</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>300</v>
+      </c>
+      <c r="E95" t="n">
+        <v>20</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L95" t="n">
+        <v>15</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>HG16688</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>300</v>
+      </c>
+      <c r="E96" t="n">
+        <v>20</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L96" t="n">
+        <v>15</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>HG16689</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>300</v>
+      </c>
+      <c r="E97" t="n">
+        <v>20</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L97" t="n">
+        <v>15</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>HG16690</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>300</v>
+      </c>
+      <c r="E98" t="n">
+        <v>20</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L98" t="n">
+        <v>15</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>HG16691</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>300</v>
+      </c>
+      <c r="E99" t="n">
+        <v>20</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L99" t="n">
+        <v>15</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>HG16692</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>300</v>
+      </c>
+      <c r="E100" t="n">
+        <v>20</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L100" t="n">
+        <v>15</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>HG16693</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>300</v>
+      </c>
+      <c r="E101" t="n">
+        <v>20</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L101" t="n">
+        <v>15</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>HG16694</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>300</v>
+      </c>
+      <c r="E102" t="n">
+        <v>20</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L102" t="n">
+        <v>15</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>HG16695</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>300</v>
+      </c>
+      <c r="E103" t="n">
+        <v>20</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L103" t="n">
+        <v>15</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>HG16696</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>300</v>
+      </c>
+      <c r="E104" t="n">
+        <v>20</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L104" t="n">
+        <v>15</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>HG16697</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>300</v>
+      </c>
+      <c r="E105" t="n">
+        <v>20</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L105" t="n">
+        <v>15</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>HG16698</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>HG103C9</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>225</v>
+      </c>
+      <c r="E106" t="n">
+        <v>15</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>A1A1</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Zapatera de Tela 9 Peldaños Marino</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>7503044894053</v>
+      </c>
+      <c r="L106" t="n">
+        <v>15</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>HG16699</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>560</v>
+      </c>
+      <c r="E107" t="n">
+        <v>28</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L107" t="n">
+        <v>20</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>P912</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>HG16700</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>560</v>
+      </c>
+      <c r="E108" t="n">
+        <v>28</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L108" t="n">
+        <v>20</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>P912</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>HG16701</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>560</v>
+      </c>
+      <c r="E109" t="n">
+        <v>28</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L109" t="n">
+        <v>20</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>P912</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>HG16702</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>560</v>
+      </c>
+      <c r="E110" t="n">
+        <v>28</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L110" t="n">
+        <v>20</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>P912</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>HG16703</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>560</v>
+      </c>
+      <c r="E111" t="n">
+        <v>28</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L111" t="n">
+        <v>20</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>P912</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>HG16704</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>560</v>
+      </c>
+      <c r="E112" t="n">
+        <v>28</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L112" t="n">
+        <v>20</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>P912</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>HG16705</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>560</v>
+      </c>
+      <c r="E113" t="n">
+        <v>28</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L113" t="n">
+        <v>20</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>P912</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>HG16706</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>560</v>
+      </c>
+      <c r="E114" t="n">
+        <v>28</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L114" t="n">
+        <v>20</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>P912</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>HG16707</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>560</v>
+      </c>
+      <c r="E115" t="n">
+        <v>28</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L115" t="n">
+        <v>20</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>P912</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>HG16708</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>560</v>
+      </c>
+      <c r="E116" t="n">
+        <v>28</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L116" t="n">
+        <v>20</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>P912</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>HG16709</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>560</v>
+      </c>
+      <c r="E117" t="n">
+        <v>28</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L117" t="n">
+        <v>20</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>P912</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>HG16710</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>560</v>
+      </c>
+      <c r="E118" t="n">
+        <v>28</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L118" t="n">
+        <v>20</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>P912</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>HG16711</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>560</v>
+      </c>
+      <c r="E119" t="n">
+        <v>28</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L119" t="n">
+        <v>20</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>P912</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>HG16712</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>560</v>
+      </c>
+      <c r="E120" t="n">
+        <v>28</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L120" t="n">
+        <v>20</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>P912</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>HG16713</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>200</v>
+      </c>
+      <c r="E121" t="n">
+        <v>10</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L121" t="n">
+        <v>20</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>P912</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>HG16714</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>560</v>
+      </c>
+      <c r="E122" t="n">
+        <v>28</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L122" t="n">
+        <v>20</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>HG16715</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>560</v>
+      </c>
+      <c r="E123" t="n">
+        <v>28</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L123" t="n">
+        <v>20</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>HG16716</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>560</v>
+      </c>
+      <c r="E124" t="n">
+        <v>28</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L124" t="n">
+        <v>20</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>HG16717</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>560</v>
+      </c>
+      <c r="E125" t="n">
+        <v>28</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L125" t="n">
+        <v>20</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>HG16718</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>560</v>
+      </c>
+      <c r="E126" t="n">
+        <v>28</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L126" t="n">
+        <v>20</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>HG16719</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>560</v>
+      </c>
+      <c r="E127" t="n">
+        <v>28</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L127" t="n">
+        <v>20</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>HG16720</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>560</v>
+      </c>
+      <c r="E128" t="n">
+        <v>28</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L128" t="n">
+        <v>20</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>HG16721</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>560</v>
+      </c>
+      <c r="E129" t="n">
+        <v>28</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L129" t="n">
+        <v>20</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>HG16722</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>560</v>
+      </c>
+      <c r="E130" t="n">
+        <v>28</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L130" t="n">
+        <v>20</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>HG16723</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>560</v>
+      </c>
+      <c r="E131" t="n">
+        <v>28</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L131" t="n">
+        <v>20</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>HG16724</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>560</v>
+      </c>
+      <c r="E132" t="n">
+        <v>28</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L132" t="n">
+        <v>20</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>HG16725</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>560</v>
+      </c>
+      <c r="E133" t="n">
+        <v>28</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L133" t="n">
+        <v>20</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>HG16726</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>560</v>
+      </c>
+      <c r="E134" t="n">
+        <v>28</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L134" t="n">
+        <v>20</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>HG16727</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>560</v>
+      </c>
+      <c r="E135" t="n">
+        <v>28</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L135" t="n">
+        <v>20</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>HG16728</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>200</v>
+      </c>
+      <c r="E136" t="n">
+        <v>10</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K136" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L136" t="n">
+        <v>20</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>HG16729</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>560</v>
+      </c>
+      <c r="E137" t="n">
+        <v>28</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K137" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L137" t="n">
+        <v>20</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>HG16730</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>560</v>
+      </c>
+      <c r="E138" t="n">
+        <v>28</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K138" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L138" t="n">
+        <v>20</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>HG16731</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>560</v>
+      </c>
+      <c r="E139" t="n">
+        <v>28</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L139" t="n">
+        <v>20</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>HG16732</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>560</v>
+      </c>
+      <c r="E140" t="n">
+        <v>28</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L140" t="n">
+        <v>20</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>HG16733</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>560</v>
+      </c>
+      <c r="E141" t="n">
+        <v>28</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L141" t="n">
+        <v>20</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>HG16734</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>560</v>
+      </c>
+      <c r="E142" t="n">
+        <v>28</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L142" t="n">
+        <v>20</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>HG16735</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>560</v>
+      </c>
+      <c r="E143" t="n">
+        <v>28</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L143" t="n">
+        <v>20</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>HG16736</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>560</v>
+      </c>
+      <c r="E144" t="n">
+        <v>28</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L144" t="n">
+        <v>20</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>HG16737</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>560</v>
+      </c>
+      <c r="E145" t="n">
+        <v>28</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L145" t="n">
+        <v>20</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>HG16738</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>560</v>
+      </c>
+      <c r="E146" t="n">
+        <v>28</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L146" t="n">
+        <v>20</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>HG16739</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>560</v>
+      </c>
+      <c r="E147" t="n">
+        <v>28</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L147" t="n">
+        <v>20</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>HG16740</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>560</v>
+      </c>
+      <c r="E148" t="n">
+        <v>28</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L148" t="n">
+        <v>20</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>HG16741</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>560</v>
+      </c>
+      <c r="E149" t="n">
+        <v>28</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K149" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L149" t="n">
+        <v>20</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>HG16742</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>560</v>
+      </c>
+      <c r="E150" t="n">
+        <v>28</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L150" t="n">
+        <v>20</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>HG16743</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>HG49C22</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>200</v>
+      </c>
+      <c r="E151" t="n">
+        <v>10</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Sabanas Queen Lisas Rosa de 52*33*37 cm</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
+        <v>7503040000000</v>
+      </c>
+      <c r="L151" t="n">
+        <v>20</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>OT30</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11</v>
+      </c>
+      <c r="E152" t="n">
+        <v>11</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>OT31</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>11</v>
+      </c>
+      <c r="E153" t="n">
+        <v>11</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K153" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>OT32</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>11</v>
+      </c>
+      <c r="E154" t="n">
+        <v>11</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K154" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>OT33</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>11</v>
+      </c>
+      <c r="E155" t="n">
+        <v>11</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K155" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>OT34</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>11</v>
+      </c>
+      <c r="E156" t="n">
+        <v>11</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K156" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>OT35</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>11</v>
+      </c>
+      <c r="E157" t="n">
+        <v>11</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K157" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>OT36</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>11</v>
+      </c>
+      <c r="E158" t="n">
+        <v>11</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K158" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>OT37</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>11</v>
+      </c>
+      <c r="E159" t="n">
+        <v>11</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K159" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>OT38</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>11</v>
+      </c>
+      <c r="E160" t="n">
+        <v>11</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K160" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>OT39</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>11</v>
+      </c>
+      <c r="E161" t="n">
+        <v>11</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K161" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>OT40</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>11</v>
+      </c>
+      <c r="E162" t="n">
+        <v>11</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K162" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>OT41</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>11</v>
+      </c>
+      <c r="E163" t="n">
+        <v>11</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K163" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>OT42</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>11</v>
+      </c>
+      <c r="E164" t="n">
+        <v>11</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K164" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>OT43</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>11</v>
+      </c>
+      <c r="E165" t="n">
+        <v>11</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K165" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>OT44</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>5</v>
+      </c>
+      <c r="E166" t="n">
+        <v>5</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K166" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>OT45</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>11</v>
+      </c>
+      <c r="E167" t="n">
+        <v>11</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K167" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>OT46</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>11</v>
+      </c>
+      <c r="E168" t="n">
+        <v>11</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K168" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>OT47</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>11</v>
+      </c>
+      <c r="E169" t="n">
+        <v>11</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K169" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>OT48</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>11</v>
+      </c>
+      <c r="E170" t="n">
+        <v>11</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K170" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>OT49</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>11</v>
+      </c>
+      <c r="E171" t="n">
+        <v>11</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K171" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>OT50</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>11</v>
+      </c>
+      <c r="E172" t="n">
+        <v>11</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K172" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>OT51</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>11</v>
+      </c>
+      <c r="E173" t="n">
+        <v>11</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K173" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>OT52</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>11</v>
+      </c>
+      <c r="E174" t="n">
+        <v>11</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K174" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>OT53</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>11</v>
+      </c>
+      <c r="E175" t="n">
+        <v>11</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K175" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>OT54</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>11</v>
+      </c>
+      <c r="E176" t="n">
+        <v>11</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K176" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>OT55</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>11</v>
+      </c>
+      <c r="E177" t="n">
+        <v>11</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K177" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>OT56</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>11</v>
+      </c>
+      <c r="E178" t="n">
+        <v>11</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K178" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>OT57</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>11</v>
+      </c>
+      <c r="E179" t="n">
+        <v>11</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K179" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>OT58</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>11</v>
+      </c>
+      <c r="E180" t="n">
+        <v>11</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K180" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>OT59</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>OT6C6</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>5</v>
+      </c>
+      <c r="E181" t="n">
+        <v>5</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>ASDF1234567</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Bicicleta Urbana de Paseo Rodada 26 Blanca</t>
+        </is>
+      </c>
+      <c r="K181" t="n">
+        <v>7503050822484</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>SA45</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E182" t="n">
+        <v>120</v>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>ZXCV0987654</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K182" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L182" t="n">
+        <v>10</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>P0911</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>SA46</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E183" t="n">
+        <v>120</v>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>ZXCV0987654</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K183" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L183" t="n">
+        <v>10</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>P0911</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>SA47</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E184" t="n">
+        <v>120</v>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>ZXCV0987654</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K184" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L184" t="n">
+        <v>10</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>P0911</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>SA48</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E185" t="n">
+        <v>120</v>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>ZXCV0987654</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K185" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L185" t="n">
+        <v>10</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>P0911</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>SA49</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E186" t="n">
+        <v>120</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>ZXCV0987654</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K186" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L186" t="n">
+        <v>10</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>P0911</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>SA50</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E187" t="n">
+        <v>120</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>ZXCV0987654</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K187" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L187" t="n">
+        <v>10</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>P0911</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>SA51</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E188" t="n">
+        <v>120</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>ZXCV0987654</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K188" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L188" t="n">
+        <v>10</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>P0911</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>SA52</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E189" t="n">
+        <v>120</v>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>ZXCV0987654</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K189" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L189" t="n">
+        <v>10</v>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>P0911</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>SA53</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E190" t="n">
+        <v>120</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>ZXCV0987654</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K190" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L190" t="n">
+        <v>10</v>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>P0911</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>SA54</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E191" t="n">
+        <v>120</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>ZXCV0987654</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K191" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L191" t="n">
+        <v>10</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>P0911</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>SA55</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E192" t="n">
+        <v>120</v>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>ZXCV0987654</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K192" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L192" t="n">
+        <v>10</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>P0911</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>SA56</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E193" t="n">
+        <v>120</v>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>ZXCV0987654</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K193" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L193" t="n">
+        <v>10</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>P0911</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>SA57</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E194" t="n">
+        <v>120</v>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>ZXCV0987654</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K194" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L194" t="n">
+        <v>10</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>P0911</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>SA58</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E195" t="n">
+        <v>120</v>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>ZXCV0987654</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K195" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L195" t="n">
+        <v>10</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>P0911</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>SA59</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="n">
+        <v>500</v>
+      </c>
+      <c r="E196" t="n">
+        <v>50</v>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>ZXCV0987654</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K196" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L196" t="n">
+        <v>10</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>P0911</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>SA60</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E197" t="n">
+        <v>120</v>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K197" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L197" t="n">
+        <v>10</v>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>P09111</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>SA61</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E198" t="n">
+        <v>120</v>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K198" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L198" t="n">
+        <v>10</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>P09111</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>SA62</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E199" t="n">
+        <v>120</v>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K199" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L199" t="n">
+        <v>10</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>P09111</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>SA63</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E200" t="n">
+        <v>120</v>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K200" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L200" t="n">
+        <v>10</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>P09111</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>SA64</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E201" t="n">
+        <v>120</v>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K201" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L201" t="n">
+        <v>10</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>P09111</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>SA65</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E202" t="n">
+        <v>120</v>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K202" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L202" t="n">
+        <v>10</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>P09111</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>SA66</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E203" t="n">
+        <v>120</v>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K203" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L203" t="n">
+        <v>10</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>P09111</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>SA67</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E204" t="n">
+        <v>120</v>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K204" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L204" t="n">
+        <v>10</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>P09111</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>SA68</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E205" t="n">
+        <v>120</v>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K205" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L205" t="n">
+        <v>10</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>P09111</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>SA69</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E206" t="n">
+        <v>120</v>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K206" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L206" t="n">
+        <v>10</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>P09111</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>SA70</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E207" t="n">
+        <v>120</v>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K207" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L207" t="n">
+        <v>10</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>P09111</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>SA71</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E208" t="n">
+        <v>120</v>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K208" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L208" t="n">
+        <v>10</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>P09111</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>SA72</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E209" t="n">
+        <v>120</v>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K209" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L209" t="n">
+        <v>10</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>P09111</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>SA73</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E210" t="n">
+        <v>120</v>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K210" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L210" t="n">
+        <v>10</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>P09111</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>SA74</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="n">
+        <v>500</v>
+      </c>
+      <c r="E211" t="n">
+        <v>50</v>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>SA7C1</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Guante De Vinyl Talla M Negro</t>
+        </is>
+      </c>
+      <c r="K211" t="n">
+        <v>7503041930822</v>
+      </c>
+      <c r="L211" t="n">
+        <v>10</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>P09111</t>
         </is>
       </c>
     </row>

--- a/files/Pruebas_Excel.xlsx
+++ b/files/Pruebas_Excel.xlsx
@@ -377,7 +377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N211"/>
+  <dimension ref="A1:N266"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="9.140625" customWidth="1" style="1" min="1" max="2"/>
@@ -9431,14 +9431,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr"/>
       <c r="D182" t="n">
         <v>1200</v>
       </c>
       <c r="E182" t="n">
         <v>120</v>
       </c>
-      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -9482,14 +9480,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
       <c r="D183" t="n">
         <v>1200</v>
       </c>
       <c r="E183" t="n">
         <v>120</v>
       </c>
-      <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -9533,14 +9529,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
       <c r="D184" t="n">
         <v>1200</v>
       </c>
       <c r="E184" t="n">
         <v>120</v>
       </c>
-      <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -9584,14 +9578,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr"/>
       <c r="D185" t="n">
         <v>1200</v>
       </c>
       <c r="E185" t="n">
         <v>120</v>
       </c>
-      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -9635,14 +9627,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
       <c r="D186" t="n">
         <v>1200</v>
       </c>
       <c r="E186" t="n">
         <v>120</v>
       </c>
-      <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -9686,14 +9676,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr"/>
       <c r="D187" t="n">
         <v>1200</v>
       </c>
       <c r="E187" t="n">
         <v>120</v>
       </c>
-      <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -9737,14 +9725,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
       <c r="D188" t="n">
         <v>1200</v>
       </c>
       <c r="E188" t="n">
         <v>120</v>
       </c>
-      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -9788,14 +9774,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
       <c r="D189" t="n">
         <v>1200</v>
       </c>
       <c r="E189" t="n">
         <v>120</v>
       </c>
-      <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -9839,14 +9823,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr"/>
       <c r="D190" t="n">
         <v>1200</v>
       </c>
       <c r="E190" t="n">
         <v>120</v>
       </c>
-      <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -9890,14 +9872,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr"/>
       <c r="D191" t="n">
         <v>1200</v>
       </c>
       <c r="E191" t="n">
         <v>120</v>
       </c>
-      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -9941,14 +9921,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
       <c r="D192" t="n">
         <v>1200</v>
       </c>
       <c r="E192" t="n">
         <v>120</v>
       </c>
-      <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -9992,14 +9970,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
       <c r="D193" t="n">
         <v>1200</v>
       </c>
       <c r="E193" t="n">
         <v>120</v>
       </c>
-      <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10043,14 +10019,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr"/>
       <c r="D194" t="n">
         <v>1200</v>
       </c>
       <c r="E194" t="n">
         <v>120</v>
       </c>
-      <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10094,14 +10068,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr"/>
       <c r="D195" t="n">
         <v>1200</v>
       </c>
       <c r="E195" t="n">
         <v>120</v>
       </c>
-      <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10145,14 +10117,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr"/>
       <c r="D196" t="n">
         <v>500</v>
       </c>
       <c r="E196" t="n">
         <v>50</v>
       </c>
-      <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10196,14 +10166,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr"/>
       <c r="D197" t="n">
         <v>1200</v>
       </c>
       <c r="E197" t="n">
         <v>120</v>
       </c>
-      <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10247,14 +10215,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr"/>
       <c r="D198" t="n">
         <v>1200</v>
       </c>
       <c r="E198" t="n">
         <v>120</v>
       </c>
-      <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10298,14 +10264,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr"/>
       <c r="D199" t="n">
         <v>1200</v>
       </c>
       <c r="E199" t="n">
         <v>120</v>
       </c>
-      <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10349,14 +10313,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr"/>
       <c r="D200" t="n">
         <v>1200</v>
       </c>
       <c r="E200" t="n">
         <v>120</v>
       </c>
-      <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10400,14 +10362,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr"/>
       <c r="D201" t="n">
         <v>1200</v>
       </c>
       <c r="E201" t="n">
         <v>120</v>
       </c>
-      <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10451,14 +10411,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr"/>
       <c r="D202" t="n">
         <v>1200</v>
       </c>
       <c r="E202" t="n">
         <v>120</v>
       </c>
-      <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10502,14 +10460,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr"/>
       <c r="D203" t="n">
         <v>1200</v>
       </c>
       <c r="E203" t="n">
         <v>120</v>
       </c>
-      <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10553,14 +10509,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr"/>
       <c r="D204" t="n">
         <v>1200</v>
       </c>
       <c r="E204" t="n">
         <v>120</v>
       </c>
-      <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10604,14 +10558,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr"/>
       <c r="D205" t="n">
         <v>1200</v>
       </c>
       <c r="E205" t="n">
         <v>120</v>
       </c>
-      <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10655,14 +10607,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr"/>
       <c r="D206" t="n">
         <v>1200</v>
       </c>
       <c r="E206" t="n">
         <v>120</v>
       </c>
-      <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10706,14 +10656,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr"/>
       <c r="D207" t="n">
         <v>1200</v>
       </c>
       <c r="E207" t="n">
         <v>120</v>
       </c>
-      <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10757,14 +10705,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr"/>
       <c r="D208" t="n">
         <v>1200</v>
       </c>
       <c r="E208" t="n">
         <v>120</v>
       </c>
-      <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10808,14 +10754,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr"/>
       <c r="D209" t="n">
         <v>1200</v>
       </c>
       <c r="E209" t="n">
         <v>120</v>
       </c>
-      <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10859,14 +10803,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr"/>
       <c r="D210" t="n">
         <v>1200</v>
       </c>
       <c r="E210" t="n">
         <v>120</v>
       </c>
-      <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10910,14 +10852,12 @@
           <t>SA7C1</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr"/>
       <c r="D211" t="n">
         <v>500</v>
       </c>
       <c r="E211" t="n">
         <v>50</v>
       </c>
-      <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr">
         <is>
           <t>Guante De Vinyl Talla M Negro</t>
@@ -10947,6 +10887,2811 @@
       <c r="M211" t="inlineStr">
         <is>
           <t>P09111</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>OT60</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>8</v>
+      </c>
+      <c r="E212" t="n">
+        <v>8</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>ASDF3536843</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K212" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>OT61</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>8</v>
+      </c>
+      <c r="E213" t="n">
+        <v>8</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>ASDF3536843</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K213" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>OT62</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>8</v>
+      </c>
+      <c r="E214" t="n">
+        <v>8</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>ASDF3536843</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K214" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>OT63</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>8</v>
+      </c>
+      <c r="E215" t="n">
+        <v>8</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>ASDF3536843</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K215" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>OT64</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>8</v>
+      </c>
+      <c r="E216" t="n">
+        <v>8</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>ASDF3536843</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K216" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>OT65</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>8</v>
+      </c>
+      <c r="E217" t="n">
+        <v>8</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>ASDF3536843</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K217" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>OT66</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>8</v>
+      </c>
+      <c r="E218" t="n">
+        <v>8</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>ASDF3536843</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K218" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>OT67</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>8</v>
+      </c>
+      <c r="E219" t="n">
+        <v>8</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>ASDF3536843</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K219" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>OT68</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>8</v>
+      </c>
+      <c r="E220" t="n">
+        <v>8</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>ASDF3536843</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K220" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>OT69</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>8</v>
+      </c>
+      <c r="E221" t="n">
+        <v>8</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>ASDF3536843</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K221" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>OT70</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>8</v>
+      </c>
+      <c r="E222" t="n">
+        <v>8</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>ASDF3536843</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K222" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>OT71</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>8</v>
+      </c>
+      <c r="E223" t="n">
+        <v>8</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>ASDF3536843</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K223" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>OT72</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>8</v>
+      </c>
+      <c r="E224" t="n">
+        <v>8</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>ASDF3536843</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K224" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>OT73</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>8</v>
+      </c>
+      <c r="E225" t="n">
+        <v>8</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>ASDF3536843</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K225" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>OT74</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>5</v>
+      </c>
+      <c r="E226" t="n">
+        <v>5</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>ASDF3536843</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K226" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>OT75</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>8</v>
+      </c>
+      <c r="E227" t="n">
+        <v>8</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>MNBV7653456</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K227" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>P097</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>OT76</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>8</v>
+      </c>
+      <c r="E228" t="n">
+        <v>8</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>MNBV7653456</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K228" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>P097</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>OT77</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>8</v>
+      </c>
+      <c r="E229" t="n">
+        <v>8</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>MNBV7653456</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K229" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>P097</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>OT78</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>8</v>
+      </c>
+      <c r="E230" t="n">
+        <v>8</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>MNBV7653456</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K230" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>P097</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>OT79</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>8</v>
+      </c>
+      <c r="E231" t="n">
+        <v>8</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>MNBV7653456</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K231" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>P097</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>OT80</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>8</v>
+      </c>
+      <c r="E232" t="n">
+        <v>8</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>MNBV7653456</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K232" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>P097</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>OT81</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>8</v>
+      </c>
+      <c r="E233" t="n">
+        <v>8</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>MNBV7653456</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K233" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>P097</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>OT82</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>8</v>
+      </c>
+      <c r="E234" t="n">
+        <v>8</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>MNBV7653456</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K234" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>P097</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>OT83</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>8</v>
+      </c>
+      <c r="E235" t="n">
+        <v>8</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>MNBV7653456</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K235" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>P097</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>OT84</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>OT8C37</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>5</v>
+      </c>
+      <c r="E236" t="n">
+        <v>5</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>MNBV7653456</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>Scooter 4 Ruedas Eléctrico Negro/Rojo</t>
+        </is>
+      </c>
+      <c r="K236" t="n">
+        <v>7503050822828</v>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>P097</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="n">
+        <v>144</v>
+      </c>
+      <c r="E237" t="n">
+        <v>24</v>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K237" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L237" t="n">
+        <v>6</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="n">
+        <v>144</v>
+      </c>
+      <c r="E238" t="n">
+        <v>24</v>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K238" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L238" t="n">
+        <v>6</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="n">
+        <v>144</v>
+      </c>
+      <c r="E239" t="n">
+        <v>24</v>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K239" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L239" t="n">
+        <v>6</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="n">
+        <v>144</v>
+      </c>
+      <c r="E240" t="n">
+        <v>24</v>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K240" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L240" t="n">
+        <v>6</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="n">
+        <v>144</v>
+      </c>
+      <c r="E241" t="n">
+        <v>24</v>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K241" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L241" t="n">
+        <v>6</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="n">
+        <v>144</v>
+      </c>
+      <c r="E242" t="n">
+        <v>24</v>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K242" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L242" t="n">
+        <v>6</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="n">
+        <v>144</v>
+      </c>
+      <c r="E243" t="n">
+        <v>24</v>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K243" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L243" t="n">
+        <v>6</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="n">
+        <v>144</v>
+      </c>
+      <c r="E244" t="n">
+        <v>24</v>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K244" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L244" t="n">
+        <v>6</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="n">
+        <v>144</v>
+      </c>
+      <c r="E245" t="n">
+        <v>24</v>
+      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K245" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L245" t="n">
+        <v>6</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="n">
+        <v>144</v>
+      </c>
+      <c r="E246" t="n">
+        <v>24</v>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K246" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L246" t="n">
+        <v>6</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="n">
+        <v>144</v>
+      </c>
+      <c r="E247" t="n">
+        <v>24</v>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K247" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L247" t="n">
+        <v>6</v>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="n">
+        <v>144</v>
+      </c>
+      <c r="E248" t="n">
+        <v>24</v>
+      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K248" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L248" t="n">
+        <v>6</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="n">
+        <v>144</v>
+      </c>
+      <c r="E249" t="n">
+        <v>24</v>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K249" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L249" t="n">
+        <v>6</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="n">
+        <v>144</v>
+      </c>
+      <c r="E250" t="n">
+        <v>24</v>
+      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K250" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L250" t="n">
+        <v>6</v>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="n">
+        <v>30</v>
+      </c>
+      <c r="E251" t="n">
+        <v>5</v>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K251" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L251" t="n">
+        <v>6</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="n">
+        <v>144</v>
+      </c>
+      <c r="E252" t="n">
+        <v>24</v>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K252" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L252" t="n">
+        <v>6</v>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="n">
+        <v>144</v>
+      </c>
+      <c r="E253" t="n">
+        <v>24</v>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K253" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L253" t="n">
+        <v>6</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="n">
+        <v>144</v>
+      </c>
+      <c r="E254" t="n">
+        <v>24</v>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K254" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L254" t="n">
+        <v>6</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="n">
+        <v>144</v>
+      </c>
+      <c r="E255" t="n">
+        <v>24</v>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K255" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L255" t="n">
+        <v>6</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="n">
+        <v>144</v>
+      </c>
+      <c r="E256" t="n">
+        <v>24</v>
+      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K256" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L256" t="n">
+        <v>6</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="n">
+        <v>144</v>
+      </c>
+      <c r="E257" t="n">
+        <v>24</v>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K257" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L257" t="n">
+        <v>6</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="n">
+        <v>144</v>
+      </c>
+      <c r="E258" t="n">
+        <v>24</v>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K258" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L258" t="n">
+        <v>6</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="n">
+        <v>144</v>
+      </c>
+      <c r="E259" t="n">
+        <v>24</v>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K259" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L259" t="n">
+        <v>6</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="n">
+        <v>144</v>
+      </c>
+      <c r="E260" t="n">
+        <v>24</v>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K260" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L260" t="n">
+        <v>6</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="n">
+        <v>144</v>
+      </c>
+      <c r="E261" t="n">
+        <v>24</v>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K261" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L261" t="n">
+        <v>6</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="n">
+        <v>144</v>
+      </c>
+      <c r="E262" t="n">
+        <v>24</v>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K262" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L262" t="n">
+        <v>6</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="n">
+        <v>144</v>
+      </c>
+      <c r="E263" t="n">
+        <v>24</v>
+      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K263" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L263" t="n">
+        <v>6</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="n">
+        <v>144</v>
+      </c>
+      <c r="E264" t="n">
+        <v>24</v>
+      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K264" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L264" t="n">
+        <v>6</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="n">
+        <v>144</v>
+      </c>
+      <c r="E265" t="n">
+        <v>24</v>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K265" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L265" t="n">
+        <v>6</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>HR10C5</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="n">
+        <v>30</v>
+      </c>
+      <c r="E266" t="n">
+        <v>5</v>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>PERW1235687</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>Bascula Comercial Digital 40Kg AY-EC02 Plata</t>
+        </is>
+      </c>
+      <c r="K266" t="n">
+        <v>7503049746449</v>
+      </c>
+      <c r="L266" t="n">
+        <v>6</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>P012</t>
         </is>
       </c>
     </row>
